--- a/docs/01_db/テーブル設計書.xlsx
+++ b/docs/01_db/テーブル設計書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fullness\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32CE0B62-94B6-4231-A44D-3CDB34E5CB25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFAB7B80-9A95-4E63-B628-94CC436951F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{84FD6787-AB77-4F59-8975-8A1607EFDD80}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{84FD6787-AB77-4F59-8975-8A1607EFDD80}"/>
   </bookViews>
   <sheets>
     <sheet name="社員テーブル" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="28">
   <si>
     <t>バリデーション</t>
     <phoneticPr fontId="1"/>
@@ -144,6 +144,16 @@
   </si>
   <si>
     <t>部署データ(DepartmentT)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>50字以内</t>
+    <rPh sb="2" eb="3">
+      <t>ジ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>イナイ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -210,7 +220,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -223,16 +233,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -566,15 +567,13 @@
       <c r="F2" s="1"/>
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
-      <c r="L2" s="4"/>
-      <c r="M2" s="4"/>
-      <c r="N2" s="4"/>
-      <c r="O2" s="4"/>
-      <c r="P2" s="4"/>
-      <c r="Q2" s="5"/>
-      <c r="R2" s="5"/>
-      <c r="S2" s="6"/>
-      <c r="T2" s="6"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+      <c r="Q2" s="2"/>
+      <c r="R2" s="2"/>
     </row>
     <row r="3" spans="2:20">
       <c r="B3" s="3" t="s">
@@ -604,15 +603,15 @@
       <c r="J3" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="L3" s="7"/>
-      <c r="M3" s="7"/>
-      <c r="N3" s="7"/>
-      <c r="O3" s="7"/>
-      <c r="P3" s="7"/>
-      <c r="Q3" s="7"/>
-      <c r="R3" s="7"/>
-      <c r="S3" s="7"/>
-      <c r="T3" s="7"/>
+      <c r="L3" s="4"/>
+      <c r="M3" s="4"/>
+      <c r="N3" s="4"/>
+      <c r="O3" s="4"/>
+      <c r="P3" s="4"/>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="4"/>
+      <c r="S3" s="4"/>
+      <c r="T3" s="4"/>
     </row>
     <row r="4" spans="2:20">
       <c r="B4" s="1" t="s">
@@ -637,15 +636,14 @@
       <c r="I4" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="L4" s="4"/>
-      <c r="M4" s="4"/>
-      <c r="N4" s="5"/>
-      <c r="O4" s="4"/>
-      <c r="P4" s="4"/>
-      <c r="Q4" s="4"/>
-      <c r="R4" s="4"/>
-      <c r="S4" s="4"/>
-      <c r="T4" s="6"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
+      <c r="N4" s="2"/>
+      <c r="O4" s="1"/>
+      <c r="P4" s="1"/>
+      <c r="Q4" s="1"/>
+      <c r="R4" s="1"/>
+      <c r="S4" s="1"/>
     </row>
     <row r="5" spans="2:20">
       <c r="B5" s="2"/>
@@ -666,15 +664,14 @@
       <c r="I5" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="L5" s="5"/>
-      <c r="M5" s="5"/>
-      <c r="N5" s="5"/>
-      <c r="O5" s="4"/>
-      <c r="P5" s="4"/>
-      <c r="Q5" s="4"/>
-      <c r="R5" s="4"/>
-      <c r="S5" s="4"/>
-      <c r="T5" s="6"/>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2"/>
+      <c r="N5" s="2"/>
+      <c r="O5" s="1"/>
+      <c r="P5" s="1"/>
+      <c r="Q5" s="1"/>
+      <c r="R5" s="1"/>
+      <c r="S5" s="1"/>
     </row>
     <row r="6" spans="2:20">
       <c r="B6" s="2"/>
@@ -732,7 +729,7 @@
         <v>2</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="J8" s="1" t="s">
         <v>0</v>
